--- a/ADO_NET/ADO/ADO/ADODOTNET.xlsx
+++ b/ADO_NET/ADO/ADO/ADODOTNET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\ADO_NET\ADO\ADO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34092A31-CDA0-487A-B6CB-EAAFDF821046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F32621A-0708-432C-AE60-072797ABC7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1205">
   <si>
     <t>1. What is ADO.NET</t>
   </si>
@@ -31714,6 +31714,699 @@
         <family val="3"/>
       </rPr>
       <t xml:space="preserve">].ConnectionString;    </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>namespace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ADO._4_SqlCommand</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>partial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : System.Web.UI.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//SqlDataReader rdr = cmd.ExecuteReader();</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the style of code </t>
+  </si>
+  <si>
+    <r>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page_Load</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ConfigurationManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.ConnectionStrings[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DBCS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>].ConnectionString;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.CommandText = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT TOP 5 ItemCode, ItemName, ItmsGrpCod , OnHand FROM OITM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">.Connection = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        GridView1.DataSource = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        GridView1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataBind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
     </r>
   </si>
 </sst>
@@ -31970,7 +32663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -32018,6 +32711,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -40935,7 +41631,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4993BBC-164D-46F2-BA57-4D7D11D8A163}">
-  <dimension ref="B2:B106"/>
+  <dimension ref="A2:Q157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -41341,50 +42037,303 @@
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B97" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B99" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B100" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B101" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B102" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B103" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B104" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B105" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B106" s="3" t="s">
         <v>106</v>
       </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="18"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
+      <c r="K109" s="18"/>
+      <c r="L109" s="18"/>
+      <c r="M109" s="18"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
+      <c r="P109" s="18"/>
+      <c r="Q109" s="18"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="18"/>
+      <c r="B110" s="23" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B111" s="23" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B112" s="23" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="23" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="23" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="23" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="23" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="23" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="24"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="23" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="25" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="25" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="25" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="25" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="25" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="25" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="25" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="25" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="25" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="25" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="25" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="25" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="24"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="25" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="18"/>
+      <c r="B140" s="25" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="23" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="25" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B145" s="25" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B146" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B147" s="25" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B148" s="27" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
+      <c r="I148" s="20"/>
+      <c r="J148" s="20"/>
+      <c r="K148" s="20"/>
+      <c r="L148" s="20"/>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B149" s="27" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C149" s="20"/>
+      <c r="D149" s="20"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20"/>
+      <c r="H149" s="20"/>
+      <c r="I149" s="20"/>
+      <c r="J149" s="20"/>
+      <c r="K149" s="20"/>
+      <c r="L149" s="20"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B150" s="25" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B151" s="25" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B152" s="25" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B153" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B154" s="24"/>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B155" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ADO_NET/ADO/ADO/ADODOTNET.xlsx
+++ b/ADO_NET/ADO/ADO/ADODOTNET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\ADO_NET\ADO\ADO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F32621A-0708-432C-AE60-072797ABC7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1627ED33-6342-4CE1-8B44-092B621D7487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1214">
   <si>
     <t>1. What is ADO.NET</t>
   </si>
@@ -32407,6 +32407,564 @@
         <family val="3"/>
       </rPr>
       <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ExecuteNonQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - delete grid beacause it’s a scalar object data type </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ConfigurationManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.ConnectionStrings[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DBCS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>].ConnectionString;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.CommandText = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT COUNT(ItemCode) FROM OITM "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">.Connection = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteScalar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Response.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"The Total Item Count is "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>());</t>
     </r>
   </si>
 </sst>
@@ -33014,6 +33572,57 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>172240</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8483B189-48FE-C9FB-4C5B-B1A9BC170551}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="35032"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="32575500"/>
+          <a:ext cx="5658640" cy="1343025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -41631,7 +42240,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4993BBC-164D-46F2-BA57-4D7D11D8A163}">
-  <dimension ref="A2:Q157"/>
+  <dimension ref="A2:Q169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -42334,6 +42943,62 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="18"/>
+      <c r="B157" s="2" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B159" s="23" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B160" s="23" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="25" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="25" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="25" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="25" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="25" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="25" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="24"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="25" t="s">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ADO_NET/ADO/ADO/ADODOTNET.xlsx
+++ b/ADO_NET/ADO/ADO/ADODOTNET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\ADO_NET\ADO\ADO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1627ED33-6342-4CE1-8B44-092B621D7487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B80946-2A43-4044-B477-6340231830E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1290">
   <si>
     <t>1. What is ADO.NET</t>
   </si>
@@ -32966,13 +32966,2792 @@
       </rPr>
       <t>());</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">insert the row </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.CommandText = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"INSERT INTO [dbo].[tblCities] VALUES('PATNA', 1)"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowAffected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteNonQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Response.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"The Total Row Affected is : "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowAffected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>());</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//SqlCommand cmd = new SqlCommand();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//cmd.CommandText = ("INSERT INTO [dbo].[tblCities] VALUES('PATNA', 1)");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//cmd.Connection = con;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//con.Open();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//int TotalRowAffected = cmd.ExecuteNonQuery();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//Response.Write("The Total Row Affected is : " + TotalRowAffected.ToString());</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.CommandText = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DELETE FROM [dbo].[tblCities] WHERE CityId = 29"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowDel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteNonQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowUpdated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteNonQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.CommandText = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"UPDATE [dbo].[tblCities] SET CityName = 'Rajgir' WHERE CityId=25"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Response.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"The Total Row Deleted is : "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowDel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">() + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"&lt;/br&gt;"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Response.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"The Total Row Inserted is : "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowAffected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">() + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"&lt;/br&gt;"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Response.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"The Total Row Updated is : "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TotalRowUpdated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">() + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"&lt;/br&gt;"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>btngetitm_Click</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> {</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ConfigurationManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.ConnectionStrings[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DBCS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>].ConnectionString;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">     {</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Command</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT * FROM OITM WHERE ITEMNAME LIKE '"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + TextBox1.Text + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"%'"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Command</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         GridView1.DataSource = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         GridView1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataBind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">     }</t>
+  </si>
+  <si>
+    <t>another eg</t>
+  </si>
+  <si>
+    <r>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>btngetitm_Click</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//string Command = ("SELECT ITEMCODE, ITEMNAME, ONHAND FROM OITM WHERE ITEMNAME LIKE '" + TextBox1.Text + "%'");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//SqlCommand cmd = new SqlCommand (Command, con);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//GridView1.DataSource = cmd.ExecuteReader();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//GridView1.DataBind();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// ANOTHER TABLE EXAMPLE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT * FROM tblProductInventory WHERE ProductName Like '"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            TextBox1.Text + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"%'"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>but if user type command like below then all table will be deleted</t>
+  </si>
+  <si>
+    <t>ip'; delete from tblproduct--</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- this will commit next line code syntax % </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT * FROM tblProductInventory WHERE ProductName Like @ProdName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Parameters.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AddWithValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"@ProdName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">,TextBox1.Text + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"%"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//this method required two value for parameter and % for like command</t>
+    </r>
+  </si>
+  <si>
+    <t>another  eg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//SqlCommand cmd = new SqlCommand("SELECT * FROM tblProductInventory WHERE ProductName Like @ProdName", con);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//cmd.Parameters.AddWithValue("@ProdName",TextBox1.Text + "%");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>////this method required two value for parameter and % for like command</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//con.Open();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//GridView1.DataSource = cmd.ExecuteReader();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//GridView1.DataBind();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT ItemCode , ItemName, OnHand FROM OITM WHERE ItemName Like @ItemName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Parameters.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AddWithValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"@ItemName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, TextBox1.Text + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"%"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> }</t>
+  </si>
+  <si>
+    <t>another method sql store procedure</t>
+  </si>
+  <si>
+    <t>Create Proc spGetItemName</t>
+  </si>
+  <si>
+    <t>@ItemName  VARCHAR(100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS </t>
+  </si>
+  <si>
+    <t>BEGIN</t>
+  </si>
+  <si>
+    <t>SELECT ItemCode, ItemName, OnHand FROM OITM</t>
+  </si>
+  <si>
+    <t>WHERE ItemName LIKE @ItemName + '%'</t>
+  </si>
+  <si>
+    <t>END</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>btngetitm_Click</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//SqlCommand cmd = new SqlCommand("SELECT * FROM tblProductInventory WHERE ProductName Like @ProdName", con);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//cmd.Parameters.AddWithValue("@ProdName",TextBox1.Text + "%");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>////this method required two value for parameter and % for like command</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//con.Open();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//GridView1.DataSource = cmd.ExecuteReader();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//GridView1.DataBind();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//SqlCommand cmd = new SqlCommand("SELECT ItemCode , ItemName, OnHand FROM OITM WHERE ItemName Like @ItemName", con);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//cmd.Parameters.AddWithValue("@ItemName", TextBox1.Text + "%");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// link with sql store procedure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"spGetItemName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.CommandType = System.Data.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CommandType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">.StoredProcedure; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// this method call store proc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Parameters.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AddWithValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"@ItemName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, TextBox1.Text + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"%"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>we can check command in sql profiler</t>
+  </si>
+  <si>
+    <t>no injection</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -33187,6 +35966,14 @@
       <name val="Cascadia Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -33221,7 +36008,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -33274,6 +36061,8 @@
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -33627,6 +36416,307 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>181</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>305693</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>76902</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA13F56C-A3B9-89CF-E6FB-00BE3518A712}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="34480500"/>
+          <a:ext cx="6401693" cy="5029902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>419414</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>171766</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA0E8DBA-F8A5-A4A9-C11E-5FE741CE8A05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="39814500"/>
+          <a:ext cx="2248214" cy="2267266"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>238</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>162628</xdr:colOff>
+      <xdr:row>246</xdr:row>
+      <xdr:rowOff>28792</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDDA3B8E-9537-798B-0338-AB4D61096F98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="45339000"/>
+          <a:ext cx="5039428" cy="1552792"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>248</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>486438</xdr:colOff>
+      <xdr:row>275</xdr:row>
+      <xdr:rowOff>76929</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C493DE6F-C860-A2E6-16F2-FD7D0F878357}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="47244000"/>
+          <a:ext cx="4753638" cy="5220429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>90802</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>591252</xdr:colOff>
+      <xdr:row>318</xdr:row>
+      <xdr:rowOff>143165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5779A81-DBC6-044A-D7D5-65D1D51ACCBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="3348"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="733425" y="58955302"/>
+          <a:ext cx="4125027" cy="1766863"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>321</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476572</xdr:colOff>
+      <xdr:row>335</xdr:row>
+      <xdr:rowOff>48004</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCD943BC-C06C-77EF-3B63-A3045C5D568D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="61150500"/>
+          <a:ext cx="2305372" cy="2715004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -33693,6 +36783,206 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>533900</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>86162</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3A6152-9F5A-31A4-7A5C-B22CCDBF9122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="15049500"/>
+          <a:ext cx="3581900" cy="3134162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>24089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>574758</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA866A23-F49B-E63D-B62A-A217A75174F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="18502589"/>
+          <a:ext cx="3622758" cy="1709462"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>295912</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>152767</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84C7A170-7BD0-05CA-F03B-F6C0D42EB3C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="25146000"/>
+          <a:ext cx="4563112" cy="2629267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400701</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>38478</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A0D6C3F-E78F-3A95-0616-87CB8A6AC68C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="28765500"/>
+          <a:ext cx="4667901" cy="2705478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -33755,6 +37045,306 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57754</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>143214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8CFFCB2-23C2-B845-3BB8-C764D3FE4D1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="18097500"/>
+          <a:ext cx="4324954" cy="2429214"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>177477</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>200706</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>28919</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0F51B15-A937-3199-1A7C-ADC169EED081}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619125" y="25894977"/>
+          <a:ext cx="3848781" cy="1946942"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>596</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>162267</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71386B03-D4E1-07DA-4744-C896BF9AB7C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="31480125"/>
+          <a:ext cx="4267796" cy="2448267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>6503</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>439947</xdr:colOff>
+      <xdr:row>243</xdr:row>
+      <xdr:rowOff>153348</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30E3A520-59C6-1BF7-3A23-340A1BD09D59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="771525" y="41202128"/>
+          <a:ext cx="10031622" cy="5290345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>247</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>276774</xdr:colOff>
+      <xdr:row>255</xdr:row>
+      <xdr:rowOff>152634</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DD27F3-F3B1-DF3D-DD98-519FEF217183}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="47101125"/>
+          <a:ext cx="3934374" cy="1676634"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>258</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>467811</xdr:colOff>
+      <xdr:row>277</xdr:row>
+      <xdr:rowOff>86242</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD05A303-481F-EE33-0623-381BACF09AF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="49196625"/>
+          <a:ext cx="7783011" cy="3705742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -42240,7 +45830,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4993BBC-164D-46F2-BA57-4D7D11D8A163}">
-  <dimension ref="A2:Q169"/>
+  <dimension ref="A2:Q309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -43000,6 +46590,223 @@
         <v>106</v>
       </c>
     </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="18"/>
+      <c r="B180" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B223" s="23" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B224" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B225" s="25" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B226" s="25" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B227" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B228" s="25" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B229" s="25" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B230" s="25" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B231" s="25" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B232" s="25" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B233" s="25" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B234" s="24"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B235" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B236" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B279" s="23" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B280" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B281" s="25" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B282" s="25" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B283" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B284" s="25" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B285" s="25" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B286" s="25" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B287" s="25" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B288" s="25" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B289" s="25" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B290" s="24"/>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B291" s="24"/>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B292" s="25" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B293" s="25" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B294" s="25" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B295" s="24"/>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B296" s="25" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B297" s="25" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B298" s="25" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B299" s="24"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B300" s="25" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B301" s="25" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B302" s="25" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B303" s="24"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B304" s="25" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B305" s="25" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B306" s="25" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B307" s="24"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B309" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -43008,7 +46815,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D213A66-4743-4E7F-B5F7-4EDCA513F3C4}">
-  <dimension ref="B3:B62"/>
+  <dimension ref="A3:O168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -43169,52 +46976,242 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>226</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="25" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="25" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="25" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="25" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="25" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="25" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="25" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="25" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="25" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="25" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="24"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="25" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="23" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="25" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="25" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="25" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="25" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="25" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="25" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="25" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="24"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="24"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="25" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="24"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="25" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="25" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="25" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="25" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="25" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="24"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F168" s="28" t="s">
+        <v>1253</v>
       </c>
     </row>
   </sheetData>
@@ -43228,7 +47225,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA41E1F5-5D85-42B5-BA42-ACB934FEC63D}">
-  <dimension ref="B3:B79"/>
+  <dimension ref="A3:M257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
@@ -43502,6 +47499,399 @@
     <row r="79" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B79" s="10" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="18"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B83" s="25" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B84" s="25" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B85" s="25" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B86" s="25" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B87" s="25" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B88" s="25" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B89" s="25" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B90" s="25" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B91" s="25" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B92" s="25" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B93" s="25" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B94" s="25" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="25" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="25" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="25" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="25" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="25" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="25" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="25" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="25" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="25" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="25" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="25" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="24"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="24"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="25" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="25" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="25" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="25" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="25" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="25" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="25" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="25" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A150" s="29"/>
+      <c r="B150" s="29" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C150" s="29"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="25" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="25" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="25" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="25" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="25" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="25" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="25" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="25" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="25" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="25" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="25" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="24"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="24"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="25" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="25" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="25" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="25" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="25" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="25" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="24"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="24"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="24"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="25" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="25" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="25" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="25" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="25" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="25" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" s="25" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" s="25" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" s="25" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B212" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B215" s="25" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C257" t="s">
+        <v>1289</v>
       </c>
     </row>
   </sheetData>

--- a/ADO_NET/ADO/ADO/ADODOTNET.xlsx
+++ b/ADO_NET/ADO/ADO/ADODOTNET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\ADO_NET\ADO\ADO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B80946-2A43-4044-B477-6340231830E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030BC44F-5A4C-46CB-8E21-B9DDAC7D58F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1291">
   <si>
     <t>1. What is ADO.NET</t>
   </si>
@@ -35745,6 +35745,9 @@
   </si>
   <si>
     <t>no injection</t>
+  </si>
+  <si>
+    <t>TEST STORE PROCEDURE</t>
   </si>
 </sst>
 </file>
@@ -37415,6 +37418,206 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>39206</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>172179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5012E47F-95E5-EAAA-3B06-D250597D6EAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="26955750"/>
+          <a:ext cx="7925906" cy="5220429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>400872</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>47977</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF492C5-4917-0403-F2E5-2F8CA7679C71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="33147000"/>
+          <a:ext cx="5887272" cy="2524477"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>505491</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>505</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{803AB592-9A88-3A75-F86E-7D077E7C26D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="35814000"/>
+          <a:ext cx="4772691" cy="3620005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>18929</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>477201</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>57552</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E0E9801-BA35-951B-6F43-87940BB03A00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="638175" y="39833429"/>
+          <a:ext cx="5935026" cy="2515123"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -47905,7 +48108,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEA32B94-84AC-4C7E-AB1C-342649241F87}">
-  <dimension ref="B2:B127"/>
+  <dimension ref="A2:P173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -48439,6 +48642,29 @@
     <row r="127" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A130" s="18"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="18"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="18"/>
+      <c r="H130" s="18"/>
+      <c r="I130" s="18"/>
+      <c r="J130" s="18"/>
+      <c r="K130" s="18"/>
+      <c r="L130" s="18"/>
+      <c r="M130" s="18"/>
+      <c r="N130" s="18"/>
+      <c r="O130" s="18"/>
+      <c r="P130" s="18"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>1290</v>
       </c>
     </row>
   </sheetData>

--- a/ADO_NET/ADO/ADO/ADODOTNET.xlsx
+++ b/ADO_NET/ADO/ADO/ADODOTNET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\ADO_NET\ADO\ADO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030BC44F-5A4C-46CB-8E21-B9DDAC7D58F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B605DA-380D-47BE-B9BD-81D97DE7A00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1334">
   <si>
     <t>1. What is ADO.NET</t>
   </si>
@@ -35748,6 +35748,2421 @@
   </si>
   <si>
     <t>TEST STORE PROCEDURE</t>
+  </si>
+  <si>
+    <r>
+      <t>namespace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ADO._8_SqlDataRdr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>partial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlDataRdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : System.Web.UI.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// need to open before reader</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT ITEMCODE, ITEMNAME, ONHAND FROM OITM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">               </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">// SqlDataReader rdr = new SqlDataReader(); WE CAN NOT USE </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                GridView1.DataSource =  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                GridView1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataBind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ();</t>
+    </r>
+  </si>
+  <si>
+    <t>READER NEED TO CLOSE SQL CONNECTION THEN ANOTHER METHOD FOR CLOSING THE CMD</t>
+  </si>
+  <si>
+    <r>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>partial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlDataRdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : System.Web.UI.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page_Load</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ConfigurationManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.ConnectionStrings[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DBCS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>].ConnectionString;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlConnection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// need to open before reader</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT ITEMCODE, ITEMNAME, ONHAND FROM OITM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">// SqlDataReader rdr = new SqlDataReader(); WE CAN NOT USE </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlDataReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">())  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// this method guranted close the connection</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hold data in reader and add </t>
+  </si>
+  <si>
+    <r>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> System.Data;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>partial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdreachrow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : System.Web.UI.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(); </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlCommand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SELECT ITEMCODE, ITEMNAME, ONHAND FROM OITM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>using</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SqlDataReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>cmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ExecuteReader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">())  </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                {</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataTable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataTable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">();  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// create table like tmp table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Columns.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Code"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Columns.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ItemDescription"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Columns.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Stock"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Columns.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SafetyStock"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8F08C4"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Read</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">()) </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                    { </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataRow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datarow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NewRow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ActualStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Convert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToInt32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ONHAND"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>]);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>double</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SafetyStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ActualStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> * 0.9;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datarow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Code"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ITEMCODE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>];</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datarow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ItemDescription"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>rdr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ITEMNAME"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>];</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datarow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Stock"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ActualStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">;   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>//rdr["ITEMCODE"];</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datarow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SafetyStock"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SafetyStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.Rows.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datarow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>// add all in data row</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                    }</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    GridView1.DataSource = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>newtable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    GridView1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DataBind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                }</t>
   </si>
 </sst>
 </file>
@@ -36243,6 +38658,255 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2990850</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="transactions in ado.net">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C526FED-0C73-889A-30EB-E6934AC71D8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="1714500"/>
+          <a:ext cx="2990850" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4210050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="transaction in ado.net using c#">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97E67662-37BA-323D-13E9-4AF0836AAA89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="3238500"/>
+          <a:ext cx="4210050" cy="1543050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2686050</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="transaction in ado.net c# with example">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB8158A7-1F67-00AE-1856-2A37D5466CF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="34671000"/>
+          <a:ext cx="2686050" cy="1609725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2695575</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="ado.net transaction c#">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE3153C5-579D-3B83-2422-73A1FC9D2385}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="38671500"/>
+          <a:ext cx="2695575" cy="1609725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -37626,6 +40290,61 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>30527</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>135166</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>29532</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C966981-E004-13A7-7820-6D7DD1F21CDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="628650" y="38892527"/>
+          <a:ext cx="10479316" cy="5523505"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -37748,7 +40467,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -37854,255 +40573,6 @@
         <a:xfrm>
           <a:off x="609600" y="23812500"/>
           <a:ext cx="5476875" cy="3400425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2990850</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="transactions in ado.net">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C526FED-0C73-889A-30EB-E6934AC71D8B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="609600" y="1714500"/>
-          <a:ext cx="2990850" cy="685800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>4210050</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="transaction in ado.net using c#">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97E67662-37BA-323D-13E9-4AF0836AAA89}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="609600" y="3238500"/>
-          <a:ext cx="4210050" cy="1543050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>182</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2686050</xdr:colOff>
-      <xdr:row>190</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="transaction in ado.net c# with example">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB8158A7-1F67-00AE-1856-2A37D5466CF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="609600" y="34671000"/>
-          <a:ext cx="2686050" cy="1609725"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>203</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2695575</xdr:colOff>
-      <xdr:row>211</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="ado.net transaction c#">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE3153C5-579D-3B83-2422-73A1FC9D2385}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="609600" y="38671500"/>
-          <a:ext cx="2695575" cy="1609725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -48679,7 +51149,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C00C105-95B3-45BC-8120-513ADC2A0CC6}">
-  <dimension ref="B2:B91"/>
+  <dimension ref="A2:O204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
@@ -49007,57 +51477,562 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B81" s="2" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B82" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B84" s="7" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B85" s="7" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B86" s="7" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
         <v>345</v>
       </c>
     </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="18"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
+      <c r="L94" s="18"/>
+      <c r="M94" s="18"/>
+      <c r="N94" s="18"/>
+      <c r="O94" s="18"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B96" s="23" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="25" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="25" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="25" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="25" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="25" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="25" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="25" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="25" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="24"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="25" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="25" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="25" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="25" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="24"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="25" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="24"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="25" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="24"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="23" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="25" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="25" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="25" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="25" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="25" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="25" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="24"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="25" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="25" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="25" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="25" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="25" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="25" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="25" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="24"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="25" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="24"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="24"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B145" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="18"/>
+      <c r="B147" s="18"/>
+      <c r="C147" s="18" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D147" s="18"/>
+      <c r="E147" s="18"/>
+      <c r="F147" s="18"/>
+      <c r="G147" s="18"/>
+      <c r="H147" s="18"/>
+      <c r="I147" s="18"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B149" s="23" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B150" s="23" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B151" s="23" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B152" s="23" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B153" s="23" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B154" s="23" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B155" s="23" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B156" s="23" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B157" s="23" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B158" s="24"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B159" s="23" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B160" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="25" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="25" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="25" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="25" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="25" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="25" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="25" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="25" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="25" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="24"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="25" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="25" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="25" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="25" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="25" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="25" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="25" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="25" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="24"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="25" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="25" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="25" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="24"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="25" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="25" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="24"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="25" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="25" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="25" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="25" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="25" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="24"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="25" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="24"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="25" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="25" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="24"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="25" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="24"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="24"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="25" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="25" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="25" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ADO_NET/ADO/ADO/ADODOTNET.xlsx
+++ b/ADO_NET/ADO/ADO/ADODOTNET.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B605DA-380D-47BE-B9BD-81D97DE7A00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
